--- a/separated_by_section/Consultations.xlsx
+++ b/separated_by_section/Consultations.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -3471,6 +3471,634 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>569768</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>Public Consultation on Requests for Temporary Adjustments to the Air Passenger Protection Regulations</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/consultation/public-consultation-requests-temporary-adjustments-air-passenger-protection-regulations</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/consultation/consultation-publique-sur-demandes-modification-temporaire-au-reglement-sur-protection</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Friday, December 11, 2020</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K45" s="1" t="inlineStr"/>
+      <c r="L45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N45" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>Consultation</t>
+        </is>
+      </c>
+      <c r="P45" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>570121</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>FAQs - Proposed Regulations Amending the Air Passenger Protection Regulations</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/faqs-proposed-regulations-amending-air-passenger-protection-regulations</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/faqs-projet-reglement-modifiant-reglement-sur-protection-des-passagers-aeriens</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>Friday, July 2, 2021</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="inlineStr"/>
+      <c r="L46" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="M46" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N46" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>572825</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>Proposed amendments to the APPR have been published in the Canada Gazette, Part I, for consultation</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/proposed-amendments-appr-have-been-published-canada-gazette-part-i-consultation</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/modifications-proposees-au-rppa-ont-ete-publiees-dans-partie-i-gazette-canada-pour</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Saturday, December 21, 2024</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="inlineStr"/>
+      <c r="L47" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="M47" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="N47" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>572371</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>Forward Regulatory Plan: 2024 to 2026 – Regulations amending the Air Passenger Protection Regulations (APPR)</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/forward-regulatory-plan-2024-2026-regulations-amending-air-passenger-protection-regulations-appr</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/plan-prospectif-reglementation-2024-a-2026-reglement-modifiant-reglement-sur-protection-des</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, April 2, 2024</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="inlineStr"/>
+      <c r="L48" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="M48" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="N48" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>Web page</t>
+        </is>
+      </c>
+      <c r="P48" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>568183</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>CTA releases What We Heard Report summarizing its air passenger protection consultations</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/cta-releases-what-we-heard-report-summarizing-its-air-passenger-protection-consultations</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/content/lotc-publie-rapport-ce-que-nous-avons-entendu-resumant-sa-consultation-sur-protection-des</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Monday, October 15, 2018</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>Keep</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr"/>
+      <c r="L49" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="N49" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="P49" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>568653</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>Chair and CEO Scott Streiner press conference statement on Air Passenger Protection Regulations, May 24, 2019</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/chair-and-ceo-scott-streiner-press-conference-statement-air-passenger-protection-regulations</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/annonce-president-et-premier-dirigeant-scott-streiner-lors-conference-presse-sur-reglement</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday, May 28, 2019</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>568256</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Wheels up: On our way to new protections for air passengers</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/wheels-our-way-new-protections-air-passengers</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/preparation-au-decollage-adoption-prochaine-nouvelles-mesures-protection-pour-passagers</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Thursday, November 8, 2018</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N51" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P51" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>567865</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>Statement by Canadian Transportation Agency Chair &amp; CEO Scott Streiner on the launch of the Air Passenger Protection Consultations on May 28, 2018</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/content/remarks-launch-consultations-new-air-passenger-protection-regulations</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/contenu/remarques-sur-lancement-des-consultations-sur-nouveau-reglement-sur-protection-des-passagers</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Monday, May 28, 2018</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M52" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N52" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>Speeches</t>
+        </is>
+      </c>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>565464</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Milton Logistics Hub Project</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/eng/consultation/milton-logistics-hub-project</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>https://otc-cta.gc.ca/fra/consultation/projet-pole-logistique-milton</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday, June 8, 2016</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>About / Contact / Corporate</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>Consultations</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="K53" s="1" t="inlineStr">
+        <is>
+          <t>Possibly outdated</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>Consultation</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
